--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-electronics-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-electronics-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Decoupling tụ (thường dùng tụ gốm 0.1uF) đóng vai trò là kho chứa năng lượng cục bộ cực nhanh. Khi IC hoạt động chuyển mạch tốc độ cao đòi hỏi dòng tức thời, tụ sẽ phóng điện bù đắp ngay lập tức, ngăn nhiễu tần số cao truyền ngược lại đường nguồn và chống sụt áp tức thời tại chân chip.</v>
       </c>
       <c r="F2" t="str">
+        <v>Mắc nối tiếp trực tiếp trên đường dây cấp nguồn chính của toàn mạch — mắc nối tiếp nguồn chính</v>
+      </c>
+      <c r="G2" t="str">
         <v>Mắc song song giữa chân nguồn (VCC) và chân đất (GND), đặt càng sát chân nguồn của IC càng tốt để lọc nhiễu tần số cao từ nguồn cấp — mắc song song sát chân nguồn IC</v>
       </c>
-      <c r="G2" t="str">
-        <v>Mắc nối tiếp trực tiếp trên đường dây cấp nguồn chính của toàn mạch — mắc nối tiếp nguồn chính</v>
-      </c>
       <c r="H2" t="str">
+        <v>Chỉ mắc khi hệ thống phát sinh lỗi sụt áp nguồn xuống dưới 1V — chỉ mắc khi sụt áp nặng</v>
+      </c>
+      <c r="I2" t="str">
         <v>Mắc nối tiếp với thạch anh ngoại vi để tăng tần số dao động của chip — mắc nối tiếp thạch anh</v>
       </c>
-      <c r="I2" t="str">
-        <v>Chỉ mắc khi hệ thống phát sinh lỗi sụt áp nguồn xuống dưới 1V — chỉ mắc khi sụt áp nặng</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         <v>Đóng vai trò là khóa điện tử (Switch) điều khiển dòng điện lớn bằng dòng điều khiển nhỏ, hoặc khuếch đại tín hiệu — khóa điện tử hoặc khuếch đại</v>
       </c>
       <c r="G3" t="str">
+        <v>Cho phép dòng điện chạy qua cả hai chiều hoàn toàn tự do không có cản trở — dẫn điện hai chiều</v>
+      </c>
+      <c r="H3" t="str">
         <v>Lưu trữ dữ liệu chương trình ứng dụng chính của vi điều khiển — lưu trữ chương trình</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Cho phép dòng điện chạy qua cả hai chiều hoàn toàn tự do không có cản trở — dẫn điện hai chiều</v>
       </c>
       <c r="I3" t="str">
         <v>Tự động reset lại toàn bộ hệ thống khi phát hiện có rò rỉ điện ra vỏ máy — ngắt rò rỉ điện</v>
@@ -524,19 +524,19 @@
         <v>Chế độ đo thông mạch đo điện trở thấp. Khi bấm nút, hai tiếp điểm chạm nhau tạo thành mạch kín (R ~ 0 Ohm), đồng hồ vạn năng kêu bíp để báo hiệu đường dây thông suốt.</v>
       </c>
       <c r="F4" t="str">
-        <v>Đồng hồ phát ra tiếng kêu bíp liên tục biểu thị điện trở giữa hai đầu nút bấm gần như bằng 0 (mạch kín) — kêu bíp mạch kín</v>
+        <v>Màn hình hiển thị chữ cái "FAIL" màu đỏ nhấp nháy báo động — báo động lỗi FAIL</v>
       </c>
       <c r="G4" t="str">
         <v>Đồng hồ hiển thị giá trị điện trở vô hạn (mạch hở) trên màn hình — mạch hở vô hạn</v>
       </c>
       <c r="H4" t="str">
+        <v>Đồng hồ phát ra tiếng kêu bíp liên tục biểu thị điện trở giữa hai đầu nút bấm gần như bằng 0 (mạch kín) — kêu bíp mạch kín</v>
+      </c>
+      <c r="I4" t="str">
         <v>Đồng hồ tự động xả một dòng điện mạnh làm nóng nút bấm lên — xả dòng sinh nhiệt</v>
       </c>
-      <c r="I4" t="str">
-        <v>Màn hình hiển thị chữ cái "FAIL" màu đỏ nhấp nháy báo động — báo động lỗi FAIL</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>LDO (ví dụ AMS1117-3.3) hạ áp từ 5V xuống 3.3V bằng cách tiêu tán nhiệt: $P_{loss} = (V_{in} - V_{out}) \cdot I$. Nếu sụt áp lớn và dòng cao, LDO sẽ cực kỳ nóng và lãng phí năng lượng. Switching regulator đóng ngắt dòng điện (PWM) lưu trữ năng lượng trong cuộn cảm và tụ điện, đạt hiệu suất &gt; 90% nhưng tạo ra nhiễu gợn sóng (ripple noise).</v>
       </c>
       <c r="F5" t="str">
+        <v>LDO bắt buộc phải có quạt tản nhiệt bằng chất lỏng đi kèm khi chạy — quạt tản nhiệt chất lỏng</v>
+      </c>
+      <c r="G5" t="str">
         <v>LDO ổn áp bằng cách đốt năng lượng thừa thành nhiệt năng (hiệu suất thấp, ít nhiễu); Ổn áp xung đóng ngắt tần số cao qua cuộn cảm (hiệu suất cao, nhiều nhiễu) — hiệu suất và nhiễu: tuyến tính vs xung</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>LDO chỉ dùng cho dòng điện xoay chiều; còn Ổn áp xung chỉ dùng cho dòng một chiều — phân loại dòng điện xoay chiều một chiều</v>
-      </c>
-      <c r="H5" t="str">
-        <v>LDO bắt buộc phải có quạt tản nhiệt bằng chất lỏng đi kèm khi chạy — quạt tản nhiệt chất lỏng</v>
       </c>
       <c r="I5" t="str">
         <v>LDO có giá thành đắt gấp 100 lần so với ổn áp xung trên thị trường — so sánh giá thành</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Điện áp là hiệu thế giữa hai điểm. Để đo điện áp tại bất kỳ chân nào, ta đều đo so với điểm đất GND. Tất cả các module kết nối với nhau bắt buộc phải nối chung chân GND để có chung mức tham chiếu.</v>
       </c>
       <c r="F6" t="str">
+        <v>Gate — Chân điều khiển của bóng bán dẫn hiệu ứng trường MOSFET — chân điều khiển Gate</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Gold — Đường chạy mạch đồng được mạ vàng để tăng độ dẫn điện — mạ vàng đường mạch</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Generator — Máy phát điện xoay chiều cung cấp nguồn điện chính — máy phát điện</v>
+      </c>
+      <c r="I6" t="str">
         <v>Ground — Điểm đất/điểm tham chiếu điện áp (0V) chung cho toàn bộ mạch điện — điểm đất tham chiếu 0V</v>
       </c>
-      <c r="G6" t="str">
-        <v>Generator — Máy phát điện xoay chiều cung cấp nguồn điện chính — máy phát điện</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Gate — Chân điều khiển của bóng bán dẫn hiệu ứng trường MOSFET — chân điều khiển Gate</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Gold — Đường chạy mạch đồng được mạ vàng để tăng độ dẫn điện — mạ vàng đường mạch</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -623,10 +623,10 @@
         <v>Để triệt tiêu dòng điện áp ngược cảm ứng cực lớn sinh ra khi ngắt dòng điện đột ngột, bảo vệ transistor không bị đánh thủng — flyback diode bảo vệ chống dòng điện áp ngược</v>
       </c>
       <c r="G7" t="str">
+        <v>Để tăng cường lực hút nam châm điện của rơ-le lên gấp hai lần — tăng lực hút nam châm</v>
+      </c>
+      <c r="H7" t="str">
         <v>Để chuyển đổi toàn bộ dòng điện một chiều sang dòng điện xoay chiều — nghịch lưu dòng điện</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Để tăng cường lực hút nam châm điện của rơ-le lên gấp hai lần — tăng lực hút nam châm</v>
       </c>
       <c r="I7" t="str">
         <v>Để đảm bảo rơ-le tự động đóng ngắt theo đúng tần số xung nhịp SysTick — đồng bộ rơ-le</v>
@@ -652,19 +652,19 @@
         <v>Mạch 4 lớp (4-layer PCB) phổ biến cho thiết kế nhúng: 2 lớp ngoài chạy tín hiệu, 1 lớp trong làm mặt phẳng đất (GND Plane), 1 lớp trong làm mặt phẳng nguồn (Power Plane), giúp giảm thiểu nhiễu và định tuyến dây dễ dàng.</v>
       </c>
       <c r="F8" t="str">
+        <v>Single-sided hoàn toàn làm bằng giấy; còn Multi-layer làm bằng sợi thủy tinh FR4 — phân loại chất liệu</v>
+      </c>
+      <c r="G8" t="str">
         <v>Single-sided có 1 lớp đồng; Double-sided có 2 lớp đồng (trên/dưới); Multi-layer có nhiều lớp đồng (thường 4, 6, 8 lớp) ép chồng lên nhau xen kẽ lớp cách điện — phân loại theo số lớp đồng PCB</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Single-sided chỉ hỗ trợ hàn linh kiện cắm; còn Multi-layer chỉ hỗ trợ linh kiện dán SMD — phân loại linh kiện</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Single-sided hoàn toàn làm bằng giấy; còn Multi-layer làm bằng sợi thủy tinh FR4 — phân loại chất liệu</v>
       </c>
       <c r="I8" t="str">
         <v>Single-sided bắt buộc phải có hình vuông; còn Multi-layer có hình tròn — hình dáng vật lý bo mạch</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>Lỗ khoan được mạ đồng bên trong dùng để kết nối điện giữa các đường mạch (traces) nằm ở các lớp (layers) đồng khác nhau — lỗ kết nối đồng xuyên lớp</v>
       </c>
       <c r="G9" t="str">
-        <v>Vị trí để cắm ăng-ten thu phát sóng không dây cho vi điều khiển — chân cắm ăng-ten</v>
+        <v>Khe rãnh dùng để người dùng cắm thẻ nhớ mở rộng vào bo mạch — khe cắm thẻ nhớ</v>
       </c>
       <c r="H9" t="str">
         <v>Ốc vít kim loại dùng để cố định bo mạch PCB vào vỏ hộp nhựa — ốc vít cố định</v>
       </c>
       <c r="I9" t="str">
-        <v>Khe rãnh dùng để người dùng cắm thẻ nhớ mở rộng vào bo mạch — khe cắm thẻ nhớ</v>
+        <v>Vị trí để cắm ăng-ten thu phát sóng không dây cho vi điều khiển — chân cắm ăng-ten</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>Optocoupler chứa 1 LED phát hồng ngoại và 1 Photo-transistor nhận ánh sáng. Không có kết nối điện vật lý giữa đầu vào và đầu ra. Sốc điện ở tầng công suất (ví dụ sét đánh vào động cơ) chỉ làm cháy bóng LED của opto chứ không thể truyền dòng điện cao thế ngược về phá hủy chip MCU.</v>
       </c>
       <c r="F10" t="str">
+        <v>Ngăn chặn ánh sáng mặt trời chiếu trực tiếp làm nóng con chip vi điều khiển — chống bức xạ nhiệt mặt trời</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Đảm bảo tốc độ truyền dữ liệu của bus UART không bị suy giảm theo thời gian — ổn định tốc độ UART</v>
+      </c>
+      <c r="H10" t="str">
         <v>Cách ly điện hoàn toàn giữa mạch điều khiển công suất thấp (MCU) và mạch công suất cao bằng tín hiệu ánh sáng, ngăn nhiễu hoặc sốc điện phá hủy MCU — cách ly quang chống sốc điện</v>
       </c>
-      <c r="G10" t="str">
-        <v>Ngăn chặn ánh sáng mặt trời chiếu trực tiếp làm nóng con chip vi điều khiển — chống bức xạ nhiệt mặt trời</v>
-      </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Tự động tăng cường độ sáng của màn hình LCD khi đi ngoài đường — điều chỉnh độ sáng LCD</v>
       </c>
-      <c r="I10" t="str">
-        <v>Đảm bảo tốc độ truyền dữ liệu của bus UART không bị suy giảm theo thời gian — ổn định tốc độ UART</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -751,13 +751,13 @@
         <v>Chuyển vạn năng sang chế độ đo A (Ampe), cắm lại que đo vào cổng 10A/mA, và mắc NỐI TIẾP đồng hồ vào đường dây dẫn cấp điện cho tải — mắc nối tiếp đo dòng</v>
       </c>
       <c r="G11" t="str">
-        <v>Chuyển vạn năng sang chế độ đo V (Volt) và mắc song song hai đầu que đo trực tiếp vào hai cực của tải — mắc song song đo áp</v>
+        <v>Kẹp trực tiếp que đo vào vỏ ngoài bằng nhựa của dây dẫn điện — đo cảm ứng vỏ nhựa</v>
       </c>
       <c r="H11" t="str">
         <v>Dùng que đo chọc trực tiếp vào chân đất GND của bo mạch và chân nguồn cấp VCC — đoản mạch nguồn</v>
       </c>
       <c r="I11" t="str">
-        <v>Kẹp trực tiếp que đo vào vỏ ngoài bằng nhựa của dây dẫn điện — đo cảm ứng vỏ nhựa</v>
+        <v>Chuyển vạn năng sang chế độ đo V (Volt) và mắc song song hai đầu que đo trực tiếp vào hai cực của tải — mắc song song đo áp</v>
       </c>
       <c r="J11">
         <v>1</v>
